--- a/files/FMCG_SKU_Master_Pricing.xlsx
+++ b/files/FMCG_SKU_Master_Pricing.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L by BU" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,26 +26,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <sz val="16"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <i val="1"/>
       <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="001F2D55"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="9"/>
+      <name val="Calibri"/>
+      <color rgb="00222222"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -55,10 +63,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F2D55"/>
+        <bgColor rgb="001F2D55"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F6FB"/>
+        <bgColor rgb="00F4F6FB"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -66,22 +81,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D7E2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D7E2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D7E2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D7E2"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,17 +488,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>FMCG SKU Master Pricing</t>
@@ -467,111 +512,1678 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FMCG_SKU_Master_Pricing.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>Source file: FMCG_SKU_Master_Pricing.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023A</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024A</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>FY2025A</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>FY2026 Plan</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Notes</t>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>FY2027F</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>FY2028F</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>FY2029F</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>FY2030F</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Revenue (RM m)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1850</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2210</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CAGR ~9%</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>-- Banking --</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>EBITDA (RM m)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>412</v>
-      </c>
-      <c r="C6" t="n">
-        <v>455</v>
-      </c>
-      <c r="D6" t="n">
-        <v>510</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Margin lift</t>
-        </is>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>12269.1</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>12401.8</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>13058.1</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>13254.5</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>13501.6</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>13597.9</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>14038</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Net Margin (%)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="C7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>13</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Above peer median</t>
-        </is>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>-7777.4</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>-7968.8</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>-8405.799999999999</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>-8356.5</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>-8863</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>-9087.299999999999</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>-8894</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>4491.7</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>4432.9</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>4652.3</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>4897.9</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>4638.6</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>4510.6</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>5144</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Note: placeholder demo data — not real Zava figures.</t>
-        </is>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>2225.1</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>2238.8</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>2336.4</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>2470.4</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>2416.6</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>2362.3</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>2518.9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>-- Insurance --</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>3857.6</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>3983.7</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>4065.8</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>4172.8</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>4229.9</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>4265.2</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>4382.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>-2543.4</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>-2584.2</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>-2651</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>-2789.3</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>-2744.6</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>-2713.8</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>-2896</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>1314.2</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>1399.5</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>1414.8</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>1383.5</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>1485.3</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>1551.4</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>1486.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>508.3</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>594.7</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>591.3</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>616.1</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>563.3</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>558.5</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>615.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>-- Healthcare Services --</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>5346.8</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>5463.8</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>5569.7</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>5787</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>5788.1</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>5815</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>6096.6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>-3395.5</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>-3621.8</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>-3644.2</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>-3811.8</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>-3770.4</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>-3834.7</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>-4030.4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>1951.3</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>1842</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>1925.5</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1975.2</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>2017.6</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>1980.3</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>2066.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>852.3</v>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>892.6</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>945.3</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>871</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>908.1</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>930.2</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>965.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>-- Industrial Manufacturing --</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>5826.7</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>5932.8</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>6255.6</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>6181.8</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>6291.8</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>6652.8</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>6650</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>-3740</v>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>-3783.5</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>-4053.7</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>-4039.3</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>-4082.4</v>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>-4317</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>-4312.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>2086.7</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>2149.3</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>2201.9</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>2142.5</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>2209.5</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>2335.8</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>2337.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>812</v>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>713.3</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>844.9</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>834.9</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>859.3</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>905.6</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>875.6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>-- Property Development --</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>4760</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>4761.7</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>4802.1</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>5078.4</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>5050</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>5193.5</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>5267.4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>-3162.5</v>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>-3140.1</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>-3190.4</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>-3361.7</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>-3358.5</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>-3396.2</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>-3502.9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>1597.4</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>1621.7</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>1611.7</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>1716.7</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>1691.4</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>1797.3</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>1764.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>1075.9</v>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>1000.7</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>1010.8</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>1076.6</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>1123.7</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>1171.1</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>-- Oil &amp; Gas (downstream) --</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>4333.2</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>4422.1</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>4543.7</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>4589.8</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>4781.9</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>4834.4</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>4965.6</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>-2878.6</v>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>-2804.9</v>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>-2921.8</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>-2916.2</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>-3141.7</v>
+      </c>
+      <c r="G37" s="8" t="n">
+        <v>-3195.1</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>-3224.6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>1454.6</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>1617.3</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>1621.8</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>1673.6</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>1640.2</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>1639.3</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>412.5</v>
+      </c>
+      <c r="C39" s="8" t="n">
+        <v>486.2</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>409.1</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>465.1</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>485.4</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>463.3</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>460.8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>-- Retail Distribution --</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>2098.1</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>2171</v>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>2228</v>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>2218.2</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>2318.4</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>2379.2</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>2404.4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>-1369.6</v>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>-1373.1</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>-1469.1</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>-1467.1</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>-1464.7</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>-1535.6</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>-1525.8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>728.5</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>798</v>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>758.9</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>751.1</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>853.6</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>843.6</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>878.5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>150.5</v>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>149.5</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>177.5</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>134.4</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>148.3</v>
+      </c>
+      <c r="G45" s="8" t="n">
+        <v>161.6</v>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>153.8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>-- Hospitality --</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>1276.9</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>1304.5</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>1337.8</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>1384.7</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>1426.9</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>1439.3</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>1459.4</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>-830.3</v>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>-849.4</v>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>-881.6</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>-906</v>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>-942.2</v>
+      </c>
+      <c r="G49" s="8" t="n">
+        <v>-946.7</v>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>-951.1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>446.6</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>455.1</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>456.2</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>478.7</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>484.7</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>492.6</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>508.3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>193</v>
+      </c>
+      <c r="C51" s="8" t="n">
+        <v>214.9</v>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>211.2</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>216.2</v>
+      </c>
+      <c r="F51" s="8" t="n">
+        <v>236.1</v>
+      </c>
+      <c r="G51" s="8" t="n">
+        <v>240.5</v>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>226.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>-- Digital Infrastructure --</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>1620.8</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>1705.6</v>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>1724.9</v>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>1781.2</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>1823.3</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>1832.5</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>1850.4</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>-1084.5</v>
+      </c>
+      <c r="C55" s="8" t="n">
+        <v>-1076.5</v>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>-1100.7</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>-1162.2</v>
+      </c>
+      <c r="F55" s="8" t="n">
+        <v>-1173.6</v>
+      </c>
+      <c r="G55" s="8" t="n">
+        <v>-1226.1</v>
+      </c>
+      <c r="H55" s="8" t="n">
+        <v>-1175.8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="n">
+        <v>536.3</v>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>629.1</v>
+      </c>
+      <c r="D56" s="6" t="n">
+        <v>624.3</v>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>618.9</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>649.8</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>606.3</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>674.6</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>559.2</v>
+      </c>
+      <c r="C57" s="8" t="n">
+        <v>583.9</v>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>596.5</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>610.4</v>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>623.1</v>
+      </c>
+      <c r="G57" s="8" t="n">
+        <v>636.8</v>
+      </c>
+      <c r="H57" s="8" t="n">
+        <v>627.3</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="D58" s="6" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>33.9</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>-- Education Services --</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="n">
+        <v>817.8</v>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>860.5</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>873.2</v>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>870.3</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>903.9</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>922.8</v>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>926.5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n">
+        <v>-531.3</v>
+      </c>
+      <c r="C61" s="8" t="n">
+        <v>-544.1</v>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>-568.2</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>-560.6</v>
+      </c>
+      <c r="F61" s="8" t="n">
+        <v>-597.3</v>
+      </c>
+      <c r="G61" s="8" t="n">
+        <v>-600.4</v>
+      </c>
+      <c r="H61" s="8" t="n">
+        <v>-614.2</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n">
+        <v>286.5</v>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>316.4</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>305</v>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>309.6</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>306.6</v>
+      </c>
+      <c r="G62" s="6" t="n">
+        <v>322.3</v>
+      </c>
+      <c r="H62" s="6" t="n">
+        <v>312.3</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="C63" s="8" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="F63" s="8" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="G63" s="8" t="n">
+        <v>114.7</v>
+      </c>
+      <c r="H63" s="8" t="n">
+        <v>110.9</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G64" s="6" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H64" s="6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>-- Plantation --</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="n">
+        <v>1781.2</v>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>1754.5</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>1853.8</v>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>1877</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>1892.6</v>
+      </c>
+      <c r="G66" s="6" t="n">
+        <v>1971.3</v>
+      </c>
+      <c r="H66" s="6" t="n">
+        <v>1963.9</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="n">
+        <v>-1135.4</v>
+      </c>
+      <c r="C67" s="8" t="n">
+        <v>-1160.9</v>
+      </c>
+      <c r="D67" s="8" t="n">
+        <v>-1172.3</v>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>-1237.1</v>
+      </c>
+      <c r="F67" s="8" t="n">
+        <v>-1219.5</v>
+      </c>
+      <c r="G67" s="8" t="n">
+        <v>-1244.8</v>
+      </c>
+      <c r="H67" s="8" t="n">
+        <v>-1244.6</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n">
+        <v>645.8</v>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>593.6</v>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>681.5</v>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>639.9</v>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>673</v>
+      </c>
+      <c r="G68" s="6" t="n">
+        <v>726.5</v>
+      </c>
+      <c r="H68" s="6" t="n">
+        <v>719.3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n">
+        <v>355</v>
+      </c>
+      <c r="C69" s="8" t="n">
+        <v>334.6</v>
+      </c>
+      <c r="D69" s="8" t="n">
+        <v>336</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>349.6</v>
+      </c>
+      <c r="F69" s="8" t="n">
+        <v>358.9</v>
+      </c>
+      <c r="G69" s="8" t="n">
+        <v>389.2</v>
+      </c>
+      <c r="H69" s="8" t="n">
+        <v>374.2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="G70" s="6" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="H70" s="6" t="n">
+        <v>19.1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
